--- a/samples/corpus/full/entreprise/compliance-register/2026-04-10_registre-des-attestations-sous-traitants.xlsx
+++ b/samples/corpus/full/entreprise/compliance-register/2026-04-10_registre-des-attestations-sous-traitants.xlsx
@@ -499,10 +499,15 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46027</v>
+        <v>46120</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46029</v>
+        <v>46122</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Renouvelé avec l'attestation de vigilance</t>
+        </is>
       </c>
     </row>
     <row r="3">
